--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:16:54+00:00</t>
+    <t>2026-08-26T12:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:41:44+00:00</t>
+    <t>2026-08-26T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:00+00:00</t>
+    <t>2026-08-26T12:57:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:57:55+00:00</t>
+    <t>2026-08-26T13:02:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:02:54+00:00</t>
+    <t>2026-08-26T13:06:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:06:53+00:00</t>
+    <t>2026-08-26T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:20:27+00:00</t>
+    <t>2026-08-26T13:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:28:09+00:00</t>
+    <t>2026-08-26T13:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:31:50+00:00</t>
+    <t>2026-08-27T12:43:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:43:51+00:00</t>
+    <t>2026-08-28T07:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:28:24+00:00</t>
+    <t>2026-08-28T07:52:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:52:50+00:00</t>
+    <t>2026-08-28T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:32:44+00:00</t>
+    <t>2026-08-28T09:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,55 +61,58 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:00+00:00</t>
+    <t>2026-08-31T15:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative</t>
+    <t>NUM-DIZ</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative (https://www.medizininformatik-initiative.de)</t>
+    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
   </si>
   <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ISO 3166-1 alpha-2 zzgl. Sonderkonzepte für staatenlos und ungeklärt.</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ISO 3166-1 alpha-2 zzgl. Sonderkonzepte für staatenlos und ungeklärt.</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
@@ -422,18 +425,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:46:48+00:00</t>
+    <t>2026-08-31T16:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:02:27+00:00</t>
+    <t>2026-08-31T20:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:20:10+00:00</t>
+    <t>2026-08-31T20:24:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:24:53+00:00</t>
+    <t>2026-09-01T08:07:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:07:41+00:00</t>
+    <t>2026-09-01T08:58:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:58:43+00:00</t>
+    <t>2026-09-01T09:49:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:49:43+00:00</t>
+    <t>2026-09-01T09:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:54:08+00:00</t>
+    <t>2026-09-01T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:59:02+00:00</t>
+    <t>2026-09-01T13:10:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:10:54+00:00</t>
+    <t>2026-09-01T13:41:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:41:09+00:00</t>
+    <t>2026-09-03T13:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:48:05+00:00</t>
+    <t>2026-09-03T16:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:09:48+00:00</t>
+    <t>2026-09-04T09:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:46:57+00:00</t>
+    <t>2026-09-04T09:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-laendercodes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:58:25+00:00</t>
+    <t>2026-09-08T12:47:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
